--- a/data/harga_sembako_desktop.xlsx
+++ b/data/harga_sembako_desktop.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga Sembako" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Sembako" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,2358 +686,2358 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" t="n">
         <v>15600</v>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" t="n">
         <v>13500</v>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" t="n">
         <v>19600</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" t="n">
         <v>17500</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F2" t="n">
         <v>4900</v>
       </c>
-      <c r="G2" s="11" t="n">
+      <c r="G2" t="n">
         <v>12200</v>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H2" t="n">
         <v>46500</v>
       </c>
-      <c r="I2" s="11" t="n">
+      <c r="I2" t="n">
         <v>39100</v>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="J2" t="n">
         <v>41700</v>
       </c>
-      <c r="K2" s="11" t="n">
+      <c r="K2" t="n">
         <v>36500</v>
       </c>
-      <c r="L2" s="11" t="n">
+      <c r="L2" t="n">
         <v>15400</v>
       </c>
-      <c r="M2" s="11" t="n">
+      <c r="M2" t="n">
         <v>28900</v>
       </c>
-      <c r="N2" s="11" t="n">
+      <c r="N2" t="n">
         <v>46700</v>
       </c>
-      <c r="O2" s="11" t="n">
+      <c r="O2" t="n">
         <v>33900</v>
       </c>
-      <c r="P2" s="11" t="n">
+      <c r="P2" t="n">
         <v>62300</v>
       </c>
-      <c r="Q2" s="11" t="n">
+      <c r="Q2" t="n">
         <v>130600</v>
       </c>
-      <c r="R2" s="11" t="n">
+      <c r="R2" t="n">
         <v>198600</v>
       </c>
-      <c r="S2" s="11" t="n">
+      <c r="S2" t="n">
         <v>3100</v>
       </c>
-      <c r="T2" s="11" t="n">
+      <c r="T2" t="n">
         <v>4000</v>
       </c>
-      <c r="U2" s="11" t="n">
+      <c r="U2" t="n">
         <v>14700</v>
       </c>
-      <c r="V2" s="11" t="n">
+      <c r="V2" t="n">
         <v>14000</v>
       </c>
-      <c r="W2" s="11" t="n">
+      <c r="W2" t="n">
         <v>44400</v>
       </c>
-      <c r="X2" s="11" t="n">
+      <c r="X2" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" t="n">
         <v>14500</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" t="n">
         <v>12500</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" t="n">
         <v>19000</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" t="n">
         <v>17100</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" t="n">
         <v>4900</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" t="n">
         <v>11500</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" t="n">
         <v>46400</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" t="n">
         <v>38300</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J3" t="n">
         <v>38100</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="K3" t="n">
         <v>36400</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" t="n">
         <v>15300</v>
       </c>
-      <c r="M3" s="11" t="n">
+      <c r="M3" t="n">
         <v>27800</v>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="N3" t="n">
         <v>43400</v>
       </c>
-      <c r="O3" s="11" t="n">
+      <c r="O3" t="n">
         <v>36300</v>
       </c>
-      <c r="P3" s="11" t="n">
+      <c r="P3" t="n">
         <v>66400</v>
       </c>
-      <c r="Q3" s="11" t="n">
+      <c r="Q3" t="n">
         <v>131500</v>
       </c>
-      <c r="R3" s="11" t="n">
+      <c r="R3" t="n">
         <v>200600</v>
       </c>
-      <c r="S3" s="11" t="n">
+      <c r="S3" t="n">
         <v>2900</v>
       </c>
-      <c r="T3" s="11" t="n">
+      <c r="T3" t="n">
         <v>4000</v>
       </c>
-      <c r="U3" s="11" t="n">
+      <c r="U3" t="n">
         <v>15400</v>
       </c>
-      <c r="V3" s="11" t="n">
+      <c r="V3" t="n">
         <v>13700</v>
       </c>
-      <c r="W3" s="11" t="n">
+      <c r="W3" t="n">
         <v>46600</v>
       </c>
-      <c r="X3" s="11" t="n">
+      <c r="X3" t="n">
         <v>40900</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" t="n">
         <v>15000</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" t="n">
         <v>12600</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" t="n">
         <v>19800</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" t="n">
         <v>17100</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" t="n">
         <v>5000</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" t="n">
         <v>12100</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="H4" t="n">
         <v>45200</v>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="I4" t="n">
         <v>41900</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J4" t="n">
         <v>38300</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" t="n">
         <v>35900</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" t="n">
         <v>15400</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" t="n">
         <v>29300</v>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="N4" t="n">
         <v>46600</v>
       </c>
-      <c r="O4" s="11" t="n">
+      <c r="O4" t="n">
         <v>34500</v>
       </c>
-      <c r="P4" s="11" t="n">
+      <c r="P4" t="n">
         <v>66900</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" t="n">
         <v>123600</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" t="n">
         <v>200900</v>
       </c>
-      <c r="S4" s="11" t="n">
+      <c r="S4" t="n">
         <v>3100</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" t="n">
         <v>4000</v>
       </c>
-      <c r="U4" s="11" t="n">
+      <c r="U4" t="n">
         <v>15700</v>
       </c>
-      <c r="V4" s="11" t="n">
+      <c r="V4" t="n">
         <v>13500</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="W4" t="n">
         <v>44300</v>
       </c>
-      <c r="X4" s="11" t="n">
+      <c r="X4" t="n">
         <v>42800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" t="n">
         <v>14700</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" t="n">
         <v>13600</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" t="n">
         <v>20600</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" t="n">
         <v>17000</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" t="n">
         <v>5200</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" t="n">
         <v>12300</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" t="n">
         <v>45700</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" t="n">
         <v>40500</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" t="n">
         <v>38100</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" t="n">
         <v>34200</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" t="n">
         <v>15500</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" t="n">
         <v>28800</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" t="n">
         <v>47000</v>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="O5" t="n">
         <v>34600</v>
       </c>
-      <c r="P5" s="11" t="n">
+      <c r="P5" t="n">
         <v>63200</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" t="n">
         <v>124500</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" t="n">
         <v>191400</v>
       </c>
-      <c r="S5" s="11" t="n">
+      <c r="S5" t="n">
         <v>2900</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" t="n">
         <v>3800</v>
       </c>
-      <c r="U5" s="11" t="n">
+      <c r="U5" t="n">
         <v>14900</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="V5" t="n">
         <v>14600</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" t="n">
         <v>46400</v>
       </c>
-      <c r="X5" s="11" t="n">
+      <c r="X5" t="n">
         <v>43500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" t="n">
         <v>15500</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" t="n">
         <v>13500</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" t="n">
         <v>19600</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" t="n">
         <v>17300</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" t="n">
         <v>5200</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" t="n">
         <v>12000</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" t="n">
         <v>43700</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" t="n">
         <v>41800</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" t="n">
         <v>38200</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" t="n">
         <v>33900</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" t="n">
         <v>15300</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" t="n">
         <v>28300</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" t="n">
         <v>45700</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" t="n">
         <v>36600</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" t="n">
         <v>67500</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" t="n">
         <v>131200</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" t="n">
         <v>202200</v>
       </c>
-      <c r="S6" s="11" t="n">
+      <c r="S6" t="n">
         <v>3000</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="T6" t="n">
         <v>4200</v>
       </c>
-      <c r="U6" s="11" t="n">
+      <c r="U6" t="n">
         <v>15100</v>
       </c>
-      <c r="V6" s="11" t="n">
+      <c r="V6" t="n">
         <v>13700</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" t="n">
         <v>46500</v>
       </c>
-      <c r="X6" s="11" t="n">
+      <c r="X6" t="n">
         <v>40800</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" t="n">
         <v>15300</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" t="n">
         <v>12500</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" t="n">
         <v>20300</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" t="n">
         <v>17100</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" t="n">
         <v>5100</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" t="n">
         <v>12100</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" t="n">
         <v>45600</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" t="n">
         <v>41900</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" t="n">
         <v>39200</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" t="n">
         <v>34800</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" t="n">
         <v>15100</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" t="n">
         <v>27900</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N7" t="n">
         <v>45900</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" t="n">
         <v>36700</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" t="n">
         <v>66000</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" t="n">
         <v>129500</v>
       </c>
-      <c r="R7" s="11" t="n">
+      <c r="R7" t="n">
         <v>206500</v>
       </c>
-      <c r="S7" s="11" t="n">
+      <c r="S7" t="n">
         <v>3100</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="T7" t="n">
         <v>4100</v>
       </c>
-      <c r="U7" s="11" t="n">
+      <c r="U7" t="n">
         <v>15100</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" t="n">
         <v>14700</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" t="n">
         <v>45900</v>
       </c>
-      <c r="X7" s="11" t="n">
+      <c r="X7" t="n">
         <v>40400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" t="n">
         <v>15100</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" t="n">
         <v>13300</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" t="n">
         <v>19000</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" t="n">
         <v>16400</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" t="n">
         <v>4800</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" t="n">
         <v>12200</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" t="n">
         <v>46900</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" t="n">
         <v>39400</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" t="n">
         <v>41200</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" t="n">
         <v>35900</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" t="n">
         <v>14700</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" t="n">
         <v>28500</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="N8" t="n">
         <v>46300</v>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" t="n">
         <v>36200</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" t="n">
         <v>68100</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" t="n">
         <v>125800</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" t="n">
         <v>193300</v>
       </c>
-      <c r="S8" s="11" t="n">
+      <c r="S8" t="n">
         <v>3100</v>
       </c>
-      <c r="T8" s="11" t="n">
+      <c r="T8" t="n">
         <v>3900</v>
       </c>
-      <c r="U8" s="11" t="n">
+      <c r="U8" t="n">
         <v>14300</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="V8" t="n">
         <v>14300</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" t="n">
         <v>47200</v>
       </c>
-      <c r="X8" s="11" t="n">
+      <c r="X8" t="n">
         <v>41400</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" t="n">
         <v>14700</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" t="n">
         <v>13600</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" t="n">
         <v>19900</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" t="n">
         <v>17800</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" t="n">
         <v>4900</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" t="n">
         <v>11400</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" t="n">
         <v>43800</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" t="n">
         <v>41500</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" t="n">
         <v>38100</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" t="n">
         <v>34800</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" t="n">
         <v>14700</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" t="n">
         <v>28500</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="N9" t="n">
         <v>46900</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" t="n">
         <v>33500</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" t="n">
         <v>68100</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" t="n">
         <v>134000</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" t="n">
         <v>205400</v>
       </c>
-      <c r="S9" s="11" t="n">
+      <c r="S9" t="n">
         <v>2900</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" t="n">
         <v>4000</v>
       </c>
-      <c r="U9" s="11" t="n">
+      <c r="U9" t="n">
         <v>14800</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" t="n">
         <v>13800</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" t="n">
         <v>45600</v>
       </c>
-      <c r="X9" s="11" t="n">
+      <c r="X9" t="n">
         <v>42100</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" t="n">
         <v>14600</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" t="n">
         <v>13100</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" t="n">
         <v>20200</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" t="n">
         <v>16700</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" t="n">
         <v>4800</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" t="n">
         <v>11800</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" t="n">
         <v>43000</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" t="n">
         <v>38600</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" t="n">
         <v>39200</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="K10" t="n">
         <v>33900</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="L10" t="n">
         <v>14500</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" t="n">
         <v>28500</v>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="N10" t="n">
         <v>43700</v>
       </c>
-      <c r="O10" s="11" t="n">
+      <c r="O10" t="n">
         <v>34800</v>
       </c>
-      <c r="P10" s="11" t="n">
+      <c r="P10" t="n">
         <v>62600</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" t="n">
         <v>132200</v>
       </c>
-      <c r="R10" s="11" t="n">
+      <c r="R10" t="n">
         <v>193700</v>
       </c>
-      <c r="S10" s="11" t="n">
+      <c r="S10" t="n">
         <v>3100</v>
       </c>
-      <c r="T10" s="11" t="n">
+      <c r="T10" t="n">
         <v>3800</v>
       </c>
-      <c r="U10" s="11" t="n">
+      <c r="U10" t="n">
         <v>15700</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" t="n">
         <v>14000</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" t="n">
         <v>46500</v>
       </c>
-      <c r="X10" s="11" t="n">
+      <c r="X10" t="n">
         <v>40500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" t="n">
         <v>14900</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" t="n">
         <v>12400</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" t="n">
         <v>20900</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" t="n">
         <v>16600</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" t="n">
         <v>5100</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" t="n">
         <v>11600</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" t="n">
         <v>45600</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" t="n">
         <v>39400</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" t="n">
         <v>39100</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" t="n">
         <v>35200</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" t="n">
         <v>14300</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" t="n">
         <v>29200</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="N11" t="n">
         <v>44100</v>
       </c>
-      <c r="O11" s="11" t="n">
+      <c r="O11" t="n">
         <v>34900</v>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" t="n">
         <v>64100</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" t="n">
         <v>130100</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" t="n">
         <v>204400</v>
       </c>
-      <c r="S11" s="11" t="n">
+      <c r="S11" t="n">
         <v>2900</v>
       </c>
-      <c r="T11" s="11" t="n">
+      <c r="T11" t="n">
         <v>4200</v>
       </c>
-      <c r="U11" s="11" t="n">
+      <c r="U11" t="n">
         <v>15700</v>
       </c>
-      <c r="V11" s="11" t="n">
+      <c r="V11" t="n">
         <v>13600</v>
       </c>
-      <c r="W11" s="11" t="n">
+      <c r="W11" t="n">
         <v>46200</v>
       </c>
-      <c r="X11" s="11" t="n">
+      <c r="X11" t="n">
         <v>40200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" t="n">
         <v>14400</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" t="n">
         <v>13000</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" t="n">
         <v>19200</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" t="n">
         <v>16200</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" t="n">
         <v>5000</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" t="n">
         <v>12100</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" t="n">
         <v>47100</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" t="n">
         <v>38800</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" t="n">
         <v>40600</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" t="n">
         <v>33900</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" t="n">
         <v>14700</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" t="n">
         <v>28900</v>
       </c>
-      <c r="N12" s="11" t="n">
+      <c r="N12" t="n">
         <v>45300</v>
       </c>
-      <c r="O12" s="11" t="n">
+      <c r="O12" t="n">
         <v>34800</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" t="n">
         <v>66200</v>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" t="n">
         <v>134100</v>
       </c>
-      <c r="R12" s="11" t="n">
+      <c r="R12" t="n">
         <v>201700</v>
       </c>
-      <c r="S12" s="11" t="n">
+      <c r="S12" t="n">
         <v>2900</v>
       </c>
-      <c r="T12" s="11" t="n">
+      <c r="T12" t="n">
         <v>4100</v>
       </c>
-      <c r="U12" s="11" t="n">
+      <c r="U12" t="n">
         <v>15200</v>
       </c>
-      <c r="V12" s="11" t="n">
+      <c r="V12" t="n">
         <v>14500</v>
       </c>
-      <c r="W12" s="11" t="n">
+      <c r="W12" t="n">
         <v>46600</v>
       </c>
-      <c r="X12" s="11" t="n">
+      <c r="X12" t="n">
         <v>42600</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" t="n">
         <v>15600</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" t="n">
         <v>12400</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" t="n">
         <v>20000</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" t="n">
         <v>16500</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" t="n">
         <v>5100</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" t="n">
         <v>12400</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" t="n">
         <v>43800</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I13" t="n">
         <v>41600</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J13" t="n">
         <v>40600</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="K13" t="n">
         <v>33900</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="L13" t="n">
         <v>15400</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M13" t="n">
         <v>28500</v>
       </c>
-      <c r="N13" s="11" t="n">
+      <c r="N13" t="n">
         <v>46800</v>
       </c>
-      <c r="O13" s="11" t="n">
+      <c r="O13" t="n">
         <v>36600</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" t="n">
         <v>66900</v>
       </c>
-      <c r="Q13" s="11" t="n">
+      <c r="Q13" t="n">
         <v>133800</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" t="n">
         <v>204600</v>
       </c>
-      <c r="S13" s="11" t="n">
+      <c r="S13" t="n">
         <v>3000</v>
       </c>
-      <c r="T13" s="11" t="n">
+      <c r="T13" t="n">
         <v>4000</v>
       </c>
-      <c r="U13" s="11" t="n">
+      <c r="U13" t="n">
         <v>15100</v>
       </c>
-      <c r="V13" s="11" t="n">
+      <c r="V13" t="n">
         <v>13900</v>
       </c>
-      <c r="W13" s="11" t="n">
+      <c r="W13" t="n">
         <v>47000</v>
       </c>
-      <c r="X13" s="11" t="n">
+      <c r="X13" t="n">
         <v>40500</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" t="n">
         <v>15600</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" t="n">
         <v>12600</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" t="n">
         <v>19100</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" t="n">
         <v>17000</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" t="n">
         <v>4900</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" t="n">
         <v>12600</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" t="n">
         <v>43500</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I14" t="n">
         <v>39500</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" t="n">
         <v>41900</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" t="n">
         <v>34500</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" t="n">
         <v>15300</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" t="n">
         <v>26900</v>
       </c>
-      <c r="N14" s="11" t="n">
+      <c r="N14" t="n">
         <v>43800</v>
       </c>
-      <c r="O14" s="11" t="n">
+      <c r="O14" t="n">
         <v>34500</v>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" t="n">
         <v>66000</v>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" t="n">
         <v>126300</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" t="n">
         <v>209600</v>
       </c>
-      <c r="S14" s="11" t="n">
+      <c r="S14" t="n">
         <v>3000</v>
       </c>
-      <c r="T14" s="11" t="n">
+      <c r="T14" t="n">
         <v>3800</v>
       </c>
-      <c r="U14" s="11" t="n">
+      <c r="U14" t="n">
         <v>14400</v>
       </c>
-      <c r="V14" s="11" t="n">
+      <c r="V14" t="n">
         <v>14100</v>
       </c>
-      <c r="W14" s="11" t="n">
+      <c r="W14" t="n">
         <v>46700</v>
       </c>
-      <c r="X14" s="11" t="n">
+      <c r="X14" t="n">
         <v>41900</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" t="n">
         <v>14300</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" t="n">
         <v>13400</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" t="n">
         <v>20100</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" t="n">
         <v>17100</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" t="n">
         <v>4800</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" t="n">
         <v>11600</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" t="n">
         <v>45200</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" t="n">
         <v>40800</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" t="n">
         <v>39800</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" t="n">
         <v>35700</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" t="n">
         <v>15500</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" t="n">
         <v>28200</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" t="n">
         <v>46200</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" t="n">
         <v>35000</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" t="n">
         <v>66200</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" t="n">
         <v>129300</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" t="n">
         <v>203700</v>
       </c>
-      <c r="S15" s="11" t="n">
+      <c r="S15" t="n">
         <v>2900</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="T15" t="n">
         <v>3900</v>
       </c>
-      <c r="U15" s="11" t="n">
+      <c r="U15" t="n">
         <v>15300</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" t="n">
         <v>14700</v>
       </c>
-      <c r="W15" s="11" t="n">
+      <c r="W15" t="n">
         <v>43600</v>
       </c>
-      <c r="X15" s="11" t="n">
+      <c r="X15" t="n">
         <v>43700</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" t="n">
         <v>15300</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" t="n">
         <v>12800</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" t="n">
         <v>19800</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" t="n">
         <v>16500</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" t="n">
         <v>4800</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" t="n">
         <v>11900</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" t="n">
         <v>45900</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" t="n">
         <v>41600</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" t="n">
         <v>40100</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" t="n">
         <v>36600</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" t="n">
         <v>14400</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" t="n">
         <v>27800</v>
       </c>
-      <c r="N16" s="11" t="n">
+      <c r="N16" t="n">
         <v>43800</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" t="n">
         <v>34700</v>
       </c>
-      <c r="P16" s="11" t="n">
+      <c r="P16" t="n">
         <v>64300</v>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" t="n">
         <v>133100</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" t="n">
         <v>194100</v>
       </c>
-      <c r="S16" s="11" t="n">
+      <c r="S16" t="n">
         <v>2900</v>
       </c>
-      <c r="T16" s="11" t="n">
+      <c r="T16" t="n">
         <v>4100</v>
       </c>
-      <c r="U16" s="11" t="n">
+      <c r="U16" t="n">
         <v>15600</v>
       </c>
-      <c r="V16" s="11" t="n">
+      <c r="V16" t="n">
         <v>14100</v>
       </c>
-      <c r="W16" s="11" t="n">
+      <c r="W16" t="n">
         <v>45200</v>
       </c>
-      <c r="X16" s="11" t="n">
+      <c r="X16" t="n">
         <v>41900</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" t="n">
         <v>15200</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" t="n">
         <v>13100</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" t="n">
         <v>19500</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" t="n">
         <v>17400</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" t="n">
         <v>5200</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" t="n">
         <v>12200</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" t="n">
         <v>45100</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" t="n">
         <v>38900</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" t="n">
         <v>40100</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" t="n">
         <v>34400</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" t="n">
         <v>14700</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" t="n">
         <v>27300</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" t="n">
         <v>46900</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" t="n">
         <v>35200</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" t="n">
         <v>66400</v>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" t="n">
         <v>127300</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" t="n">
         <v>200500</v>
       </c>
-      <c r="S17" s="11" t="n">
+      <c r="S17" t="n">
         <v>2900</v>
       </c>
-      <c r="T17" s="11" t="n">
+      <c r="T17" t="n">
         <v>4100</v>
       </c>
-      <c r="U17" s="11" t="n">
+      <c r="U17" t="n">
         <v>14700</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" t="n">
         <v>14400</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" t="n">
         <v>44300</v>
       </c>
-      <c r="X17" s="11" t="n">
+      <c r="X17" t="n">
         <v>43100</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" t="n">
         <v>15100</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" t="n">
         <v>12800</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" t="n">
         <v>19100</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" t="n">
         <v>16200</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" t="n">
         <v>5200</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" t="n">
         <v>12200</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" t="n">
         <v>46400</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" t="n">
         <v>38200</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" t="n">
         <v>38800</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K18" t="n">
         <v>36600</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" t="n">
         <v>15700</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" t="n">
         <v>28900</v>
       </c>
-      <c r="N18" s="11" t="n">
+      <c r="N18" t="n">
         <v>46200</v>
       </c>
-      <c r="O18" s="11" t="n">
+      <c r="O18" t="n">
         <v>33700</v>
       </c>
-      <c r="P18" s="11" t="n">
+      <c r="P18" t="n">
         <v>62300</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" t="n">
         <v>124000</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" t="n">
         <v>195900</v>
       </c>
-      <c r="S18" s="11" t="n">
+      <c r="S18" t="n">
         <v>3100</v>
       </c>
-      <c r="T18" s="11" t="n">
+      <c r="T18" t="n">
         <v>4000</v>
       </c>
-      <c r="U18" s="11" t="n">
+      <c r="U18" t="n">
         <v>14700</v>
       </c>
-      <c r="V18" s="11" t="n">
+      <c r="V18" t="n">
         <v>14300</v>
       </c>
-      <c r="W18" s="11" t="n">
+      <c r="W18" t="n">
         <v>43800</v>
       </c>
-      <c r="X18" s="11" t="n">
+      <c r="X18" t="n">
         <v>44000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" t="n">
         <v>14400</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" t="n">
         <v>12600</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" t="n">
         <v>19800</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" t="n">
         <v>16700</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" t="n">
         <v>5000</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" t="n">
         <v>12600</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" t="n">
         <v>44500</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" t="n">
         <v>40700</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" t="n">
         <v>41700</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" t="n">
         <v>33400</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" t="n">
         <v>15300</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" t="n">
         <v>28200</v>
       </c>
-      <c r="N19" s="11" t="n">
+      <c r="N19" t="n">
         <v>42900</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" t="n">
         <v>33500</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" t="n">
         <v>62400</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" t="n">
         <v>133600</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" t="n">
         <v>202500</v>
       </c>
-      <c r="S19" s="11" t="n">
+      <c r="S19" t="n">
         <v>3100</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" t="n">
         <v>3900</v>
       </c>
-      <c r="U19" s="11" t="n">
+      <c r="U19" t="n">
         <v>15000</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" t="n">
         <v>13700</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" t="n">
         <v>44700</v>
       </c>
-      <c r="X19" s="11" t="n">
+      <c r="X19" t="n">
         <v>42800</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" t="n">
         <v>15600</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" t="n">
         <v>13200</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" t="n">
         <v>20500</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" t="n">
         <v>16900</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" t="n">
         <v>5100</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" t="n">
         <v>11700</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" t="n">
         <v>43800</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" t="n">
         <v>38400</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" t="n">
         <v>39000</v>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="K20" t="n">
         <v>33600</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" t="n">
         <v>14500</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" t="n">
         <v>26800</v>
       </c>
-      <c r="N20" s="11" t="n">
+      <c r="N20" t="n">
         <v>45400</v>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" t="n">
         <v>35800</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" t="n">
         <v>66300</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" t="n">
         <v>128300</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" t="n">
         <v>205600</v>
       </c>
-      <c r="S20" s="11" t="n">
+      <c r="S20" t="n">
         <v>2900</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" t="n">
         <v>3900</v>
       </c>
-      <c r="U20" s="11" t="n">
+      <c r="U20" t="n">
         <v>14600</v>
       </c>
-      <c r="V20" s="11" t="n">
+      <c r="V20" t="n">
         <v>13800</v>
       </c>
-      <c r="W20" s="11" t="n">
+      <c r="W20" t="n">
         <v>43900</v>
       </c>
-      <c r="X20" s="11" t="n">
+      <c r="X20" t="n">
         <v>40300</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" t="n">
         <v>15000</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" t="n">
         <v>13400</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" t="n">
         <v>19700</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" t="n">
         <v>16200</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" t="n">
         <v>5000</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" t="n">
         <v>12200</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H21" t="n">
         <v>45700</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" t="n">
         <v>38200</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" t="n">
         <v>40200</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" t="n">
         <v>34100</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" t="n">
         <v>15100</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" t="n">
         <v>27100</v>
       </c>
-      <c r="N21" s="11" t="n">
+      <c r="N21" t="n">
         <v>45600</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" t="n">
         <v>33900</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" t="n">
         <v>67000</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" t="n">
         <v>130200</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" t="n">
         <v>208500</v>
       </c>
-      <c r="S21" s="11" t="n">
+      <c r="S21" t="n">
         <v>3100</v>
       </c>
-      <c r="T21" s="11" t="n">
+      <c r="T21" t="n">
         <v>4200</v>
       </c>
-      <c r="U21" s="11" t="n">
+      <c r="U21" t="n">
         <v>15600</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" t="n">
         <v>14200</v>
       </c>
-      <c r="W21" s="11" t="n">
+      <c r="W21" t="n">
         <v>46900</v>
       </c>
-      <c r="X21" s="11" t="n">
+      <c r="X21" t="n">
         <v>43000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" t="n">
         <v>14600</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" t="n">
         <v>12400</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" t="n">
         <v>19700</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" t="n">
         <v>16800</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" t="n">
         <v>5200</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" t="n">
         <v>12300</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H22" t="n">
         <v>45600</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" t="n">
         <v>38000</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" t="n">
         <v>38900</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" t="n">
         <v>35800</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" t="n">
         <v>14500</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" t="n">
         <v>27000</v>
       </c>
-      <c r="N22" s="11" t="n">
+      <c r="N22" t="n">
         <v>42900</v>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" t="n">
         <v>35200</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" t="n">
         <v>62200</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" t="n">
         <v>127000</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" t="n">
         <v>207000</v>
       </c>
-      <c r="S22" s="11" t="n">
+      <c r="S22" t="n">
         <v>3100</v>
       </c>
-      <c r="T22" s="11" t="n">
+      <c r="T22" t="n">
         <v>4000</v>
       </c>
-      <c r="U22" s="11" t="n">
+      <c r="U22" t="n">
         <v>14400</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" t="n">
         <v>14500</v>
       </c>
-      <c r="W22" s="11" t="n">
+      <c r="W22" t="n">
         <v>47100</v>
       </c>
-      <c r="X22" s="11" t="n">
+      <c r="X22" t="n">
         <v>42600</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" t="n">
         <v>15300</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" t="n">
         <v>13600</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" t="n">
         <v>20800</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" t="n">
         <v>17500</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" t="n">
         <v>5000</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" t="n">
         <v>11500</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H23" t="n">
         <v>42800</v>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I23" t="n">
         <v>41500</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J23" t="n">
         <v>39300</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" t="n">
         <v>36700</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" t="n">
         <v>14600</v>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="M23" t="n">
         <v>27200</v>
       </c>
-      <c r="N23" s="11" t="n">
+      <c r="N23" t="n">
         <v>47100</v>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="O23" t="n">
         <v>36100</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" t="n">
         <v>65700</v>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" t="n">
         <v>133200</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" t="n">
         <v>198800</v>
       </c>
-      <c r="S23" s="11" t="n">
+      <c r="S23" t="n">
         <v>3000</v>
       </c>
-      <c r="T23" s="11" t="n">
+      <c r="T23" t="n">
         <v>4200</v>
       </c>
-      <c r="U23" s="11" t="n">
+      <c r="U23" t="n">
         <v>15700</v>
       </c>
-      <c r="V23" s="11" t="n">
+      <c r="V23" t="n">
         <v>13300</v>
       </c>
-      <c r="W23" s="11" t="n">
+      <c r="W23" t="n">
         <v>43300</v>
       </c>
-      <c r="X23" s="11" t="n">
+      <c r="X23" t="n">
         <v>40100</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" t="n">
         <v>14600</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" t="n">
         <v>13200</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" t="n">
         <v>20800</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" t="n">
         <v>16300</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" t="n">
         <v>4800</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" t="n">
         <v>12300</v>
       </c>
-      <c r="H24" s="11" t="n">
+      <c r="H24" t="n">
         <v>47000</v>
       </c>
-      <c r="I24" s="11" t="n">
+      <c r="I24" t="n">
         <v>40200</v>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J24" t="n">
         <v>39700</v>
       </c>
-      <c r="K24" s="11" t="n">
+      <c r="K24" t="n">
         <v>36400</v>
       </c>
-      <c r="L24" s="11" t="n">
+      <c r="L24" t="n">
         <v>15000</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" t="n">
         <v>28500</v>
       </c>
-      <c r="N24" s="11" t="n">
+      <c r="N24" t="n">
         <v>43300</v>
       </c>
-      <c r="O24" s="11" t="n">
+      <c r="O24" t="n">
         <v>34400</v>
       </c>
-      <c r="P24" s="11" t="n">
+      <c r="P24" t="n">
         <v>67300</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" t="n">
         <v>125200</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" t="n">
         <v>208300</v>
       </c>
-      <c r="S24" s="11" t="n">
+      <c r="S24" t="n">
         <v>3100</v>
       </c>
-      <c r="T24" s="11" t="n">
+      <c r="T24" t="n">
         <v>3900</v>
       </c>
-      <c r="U24" s="11" t="n">
+      <c r="U24" t="n">
         <v>14400</v>
       </c>
-      <c r="V24" s="11" t="n">
+      <c r="V24" t="n">
         <v>13800</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" t="n">
         <v>46900</v>
       </c>
-      <c r="X24" s="11" t="n">
+      <c r="X24" t="n">
         <v>41700</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" t="n">
         <v>14900</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" t="n">
         <v>13600</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" t="n">
         <v>20600</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" t="n">
         <v>16200</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" t="n">
         <v>4900</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" t="n">
         <v>11500</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H25" t="n">
         <v>44300</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I25" t="n">
         <v>41200</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J25" t="n">
         <v>39300</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K25" t="n">
         <v>33800</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L25" t="n">
         <v>14500</v>
       </c>
-      <c r="M25" s="11" t="n">
+      <c r="M25" t="n">
         <v>28000</v>
       </c>
-      <c r="N25" s="11" t="n">
+      <c r="N25" t="n">
         <v>43800</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="O25" t="n">
         <v>33800</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" t="n">
         <v>64900</v>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q25" t="n">
         <v>131400</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" t="n">
         <v>208900</v>
       </c>
-      <c r="S25" s="11" t="n">
+      <c r="S25" t="n">
         <v>2900</v>
       </c>
-      <c r="T25" s="11" t="n">
+      <c r="T25" t="n">
         <v>4100</v>
       </c>
-      <c r="U25" s="11" t="n">
+      <c r="U25" t="n">
         <v>15200</v>
       </c>
-      <c r="V25" s="11" t="n">
+      <c r="V25" t="n">
         <v>13400</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" t="n">
         <v>45600</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" t="n">
         <v>42600</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" t="n">
         <v>15500</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" t="n">
         <v>12500</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" t="n">
         <v>19400</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" t="n">
         <v>16600</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" t="n">
         <v>5200</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" t="n">
         <v>12200</v>
       </c>
-      <c r="H26" s="11" t="n">
+      <c r="H26" t="n">
         <v>45000</v>
       </c>
-      <c r="I26" s="11" t="n">
+      <c r="I26" t="n">
         <v>38200</v>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="J26" t="n">
         <v>39400</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="K26" t="n">
         <v>34400</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" t="n">
         <v>15600</v>
       </c>
-      <c r="M26" s="11" t="n">
+      <c r="M26" t="n">
         <v>28900</v>
       </c>
-      <c r="N26" s="11" t="n">
+      <c r="N26" t="n">
         <v>43300</v>
       </c>
-      <c r="O26" s="11" t="n">
+      <c r="O26" t="n">
         <v>36700</v>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" t="n">
         <v>65300</v>
       </c>
-      <c r="Q26" s="11" t="n">
+      <c r="Q26" t="n">
         <v>126200</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" t="n">
         <v>207400</v>
       </c>
-      <c r="S26" s="11" t="n">
+      <c r="S26" t="n">
         <v>2900</v>
       </c>
-      <c r="T26" s="11" t="n">
+      <c r="T26" t="n">
         <v>3900</v>
       </c>
-      <c r="U26" s="11" t="n">
+      <c r="U26" t="n">
         <v>15100</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" t="n">
         <v>14400</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" t="n">
         <v>44200</v>
       </c>
-      <c r="X26" s="11" t="n">
+      <c r="X26" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" t="n">
         <v>15400</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" t="n">
         <v>12900</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" t="n">
         <v>20900</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" t="n">
         <v>16400</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" t="n">
         <v>4800</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G27" t="n">
         <v>11500</v>
       </c>
-      <c r="H27" s="11" t="n">
+      <c r="H27" t="n">
         <v>47000</v>
       </c>
-      <c r="I27" s="11" t="n">
+      <c r="I27" t="n">
         <v>40500</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J27" t="n">
         <v>41300</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="K27" t="n">
         <v>36700</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" t="n">
         <v>14700</v>
       </c>
-      <c r="M27" s="11" t="n">
+      <c r="M27" t="n">
         <v>28100</v>
       </c>
-      <c r="N27" s="11" t="n">
+      <c r="N27" t="n">
         <v>46200</v>
       </c>
-      <c r="O27" s="11" t="n">
+      <c r="O27" t="n">
         <v>36300</v>
       </c>
-      <c r="P27" s="11" t="n">
+      <c r="P27" t="n">
         <v>63300</v>
       </c>
-      <c r="Q27" s="11" t="n">
+      <c r="Q27" t="n">
         <v>126500</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" t="n">
         <v>205200</v>
       </c>
-      <c r="S27" s="11" t="n">
+      <c r="S27" t="n">
         <v>3000</v>
       </c>
-      <c r="T27" s="11" t="n">
+      <c r="T27" t="n">
         <v>4000</v>
       </c>
-      <c r="U27" s="11" t="n">
+      <c r="U27" t="n">
         <v>14400</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" t="n">
         <v>14500</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" t="n">
         <v>43200</v>
       </c>
-      <c r="X27" s="11" t="n">
+      <c r="X27" t="n">
         <v>40900</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" t="n">
         <v>14500</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" t="n">
         <v>13200</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" t="n">
         <v>19100</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" t="n">
         <v>16700</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" t="n">
         <v>4800</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" t="n">
         <v>12200</v>
       </c>
-      <c r="H28" s="11" t="n">
+      <c r="H28" t="n">
         <v>45000</v>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="I28" t="n">
         <v>40400</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" t="n">
         <v>40700</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" t="n">
         <v>34100</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" t="n">
         <v>14500</v>
       </c>
-      <c r="M28" s="11" t="n">
+      <c r="M28" t="n">
         <v>28500</v>
       </c>
-      <c r="N28" s="11" t="n">
+      <c r="N28" t="n">
         <v>44100</v>
       </c>
-      <c r="O28" s="11" t="n">
+      <c r="O28" t="n">
         <v>35800</v>
       </c>
-      <c r="P28" s="11" t="n">
+      <c r="P28" t="n">
         <v>64400</v>
       </c>
-      <c r="Q28" s="11" t="n">
+      <c r="Q28" t="n">
         <v>125100</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" t="n">
         <v>208600</v>
       </c>
-      <c r="S28" s="11" t="n">
+      <c r="S28" t="n">
         <v>3000</v>
       </c>
-      <c r="T28" s="11" t="n">
+      <c r="T28" t="n">
         <v>4200</v>
       </c>
-      <c r="U28" s="11" t="n">
+      <c r="U28" t="n">
         <v>15400</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" t="n">
         <v>14400</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" t="n">
         <v>44100</v>
       </c>
-      <c r="X28" s="11" t="n">
+      <c r="X28" t="n">
         <v>39900</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" t="n">
         <v>14900</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" t="n">
         <v>13400</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" t="n">
         <v>19300</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" t="n">
         <v>16400</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" t="n">
         <v>4800</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G29" t="n">
         <v>11800</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H29" t="n">
         <v>46200</v>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="I29" t="n">
         <v>38900</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J29" t="n">
         <v>40300</v>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="K29" t="n">
         <v>34400</v>
       </c>
-      <c r="L29" s="11" t="n">
+      <c r="L29" t="n">
         <v>14700</v>
       </c>
-      <c r="M29" s="11" t="n">
+      <c r="M29" t="n">
         <v>28500</v>
       </c>
-      <c r="N29" s="11" t="n">
+      <c r="N29" t="n">
         <v>44900</v>
       </c>
-      <c r="O29" s="11" t="n">
+      <c r="O29" t="n">
         <v>35600</v>
       </c>
-      <c r="P29" s="11" t="n">
+      <c r="P29" t="n">
         <v>68000</v>
       </c>
-      <c r="Q29" s="11" t="n">
+      <c r="Q29" t="n">
         <v>130100</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" t="n">
         <v>190400</v>
       </c>
-      <c r="S29" s="11" t="n">
+      <c r="S29" t="n">
         <v>3000</v>
       </c>
-      <c r="T29" s="11" t="n">
+      <c r="T29" t="n">
         <v>4100</v>
       </c>
-      <c r="U29" s="11" t="n">
+      <c r="U29" t="n">
         <v>14600</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" t="n">
         <v>13500</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" t="n">
         <v>46900</v>
       </c>
-      <c r="X29" s="11" t="n">
+      <c r="X29" t="n">
         <v>40800</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" t="n">
         <v>15000</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" t="n">
         <v>12700</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" t="n">
         <v>20000</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" t="n">
         <v>17400</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" t="n">
         <v>4800</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" t="n">
         <v>12400</v>
       </c>
-      <c r="H30" s="11" t="n">
+      <c r="H30" t="n">
         <v>44500</v>
       </c>
-      <c r="I30" s="11" t="n">
+      <c r="I30" t="n">
         <v>38900</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J30" t="n">
         <v>41100</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" t="n">
         <v>35600</v>
       </c>
-      <c r="L30" s="11" t="n">
+      <c r="L30" t="n">
         <v>15200</v>
       </c>
-      <c r="M30" s="11" t="n">
+      <c r="M30" t="n">
         <v>29000</v>
       </c>
-      <c r="N30" s="11" t="n">
+      <c r="N30" t="n">
         <v>43300</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" t="n">
         <v>36400</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P30" t="n">
         <v>66200</v>
       </c>
-      <c r="Q30" s="11" t="n">
+      <c r="Q30" t="n">
         <v>129600</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" t="n">
         <v>207700</v>
       </c>
-      <c r="S30" s="11" t="n">
+      <c r="S30" t="n">
         <v>3100</v>
       </c>
-      <c r="T30" s="11" t="n">
+      <c r="T30" t="n">
         <v>3800</v>
       </c>
-      <c r="U30" s="11" t="n">
+      <c r="U30" t="n">
         <v>15100</v>
       </c>
-      <c r="V30" s="11" t="n">
+      <c r="V30" t="n">
         <v>14300</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" t="n">
         <v>46100</v>
       </c>
-      <c r="X30" s="11" t="n">
+      <c r="X30" t="n">
         <v>41500</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" t="n">
         <v>14500</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" t="n">
         <v>13600</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" t="n">
         <v>19300</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" t="n">
         <v>16900</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" t="n">
         <v>5000</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" t="n">
         <v>11500</v>
       </c>
-      <c r="H31" s="11" t="n">
+      <c r="H31" t="n">
         <v>45200</v>
       </c>
-      <c r="I31" s="11" t="n">
+      <c r="I31" t="n">
         <v>41900</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J31" t="n">
         <v>40000</v>
       </c>
-      <c r="K31" s="11" t="n">
+      <c r="K31" t="n">
         <v>34900</v>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="L31" t="n">
         <v>15600</v>
       </c>
-      <c r="M31" s="11" t="n">
+      <c r="M31" t="n">
         <v>28400</v>
       </c>
-      <c r="N31" s="11" t="n">
+      <c r="N31" t="n">
         <v>43000</v>
       </c>
-      <c r="O31" s="11" t="n">
+      <c r="O31" t="n">
         <v>34800</v>
       </c>
-      <c r="P31" s="11" t="n">
+      <c r="P31" t="n">
         <v>67900</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" t="n">
         <v>125600</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" t="n">
         <v>196200</v>
       </c>
-      <c r="S31" s="11" t="n">
+      <c r="S31" t="n">
         <v>3000</v>
       </c>
-      <c r="T31" s="11" t="n">
+      <c r="T31" t="n">
         <v>4100</v>
       </c>
-      <c r="U31" s="11" t="n">
+      <c r="U31" t="n">
         <v>15400</v>
       </c>
-      <c r="V31" s="11" t="n">
+      <c r="V31" t="n">
         <v>14600</v>
       </c>
-      <c r="W31" s="11" t="n">
+      <c r="W31" t="n">
         <v>47000</v>
       </c>
-      <c r="X31" s="11" t="n">
+      <c r="X31" t="n">
         <v>40500</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" t="n">
         <v>15100</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" t="n">
         <v>12800</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" t="n">
         <v>19400</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" t="n">
         <v>17500</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" t="n">
         <v>5100</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" t="n">
         <v>11400</v>
       </c>
-      <c r="H32" s="11" t="n">
+      <c r="H32" t="n">
         <v>46500</v>
       </c>
-      <c r="I32" s="11" t="n">
+      <c r="I32" t="n">
         <v>41700</v>
       </c>
-      <c r="J32" s="11" t="n">
+      <c r="J32" t="n">
         <v>41100</v>
       </c>
-      <c r="K32" s="11" t="n">
+      <c r="K32" t="n">
         <v>35800</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="L32" t="n">
         <v>15000</v>
       </c>
-      <c r="M32" s="11" t="n">
+      <c r="M32" t="n">
         <v>29300</v>
       </c>
-      <c r="N32" s="11" t="n">
+      <c r="N32" t="n">
         <v>43600</v>
       </c>
-      <c r="O32" s="11" t="n">
+      <c r="O32" t="n">
         <v>34500</v>
       </c>
-      <c r="P32" s="11" t="n">
+      <c r="P32" t="n">
         <v>66000</v>
       </c>
-      <c r="Q32" s="11" t="n">
+      <c r="Q32" t="n">
         <v>134000</v>
       </c>
-      <c r="R32" s="11" t="n">
+      <c r="R32" t="n">
         <v>202000</v>
       </c>
-      <c r="S32" s="11" t="n">
+      <c r="S32" t="n">
         <v>3100</v>
       </c>
-      <c r="T32" s="11" t="n">
+      <c r="T32" t="n">
         <v>4100</v>
       </c>
-      <c r="U32" s="11" t="n">
+      <c r="U32" t="n">
         <v>15600</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="V32" t="n">
         <v>14500</v>
       </c>
-      <c r="W32" s="11" t="n">
+      <c r="W32" t="n">
         <v>45200</v>
       </c>
-      <c r="X32" s="11" t="n">
+      <c r="X32" t="n">
         <v>42200</v>
       </c>
     </row>
